--- a/financial_models/opportunities/not_monitored/300979.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/not_monitored/300979.SZ_Valuation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\not_monitored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DE1C0A-EF4B-48F9-8AE5-39AB7197F0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579A54EE-2C76-4952-9746-C86F4DD17E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>8.05651608340405E-2</v>
+        <v>8.8713270485525436E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,18 +5440,18 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
-        <v>2-stage DCF Valuation Conclusion</v>
+        <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>54.288928790724519</v>
+        <v>55.637212899182018</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>345</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>29.226598159949372</v>
+        <v>29.847927242187851</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>404</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>36.197435095021866</v>
+        <v>36.976227359834859</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>405</v>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>44.461141126051231</v>
+        <v>45.42753777352484</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>406</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>50.015220493730425</v>
+        <v>51.108143361888835</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>407</v>
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.3</v>
+        <v>0.30997621913985418</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591302</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>65.58 CNY</v>
+        <v>67.28 CNY</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-2.3711651808313684E-2</v>
+        <v>-2.4966507819745243E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>56.75 CNY</v>
+        <v>58.18 CNY</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.6438258161387704E-2</v>
+        <v>2.5353181897127177E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>52.82 CNY</v>
+        <v>54.13 CNY</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.2323389743423848E-2</v>
+        <v>5.1340431159478762E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>49.19 CNY</v>
+        <v>50.38 CNY</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.8735913620371217E-2</v>
+        <v>7.7867615825633618E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.83 CNY</v>
+        <v>46.92 CNY</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6458,17 +6458,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.10566314064426917</v>
+        <v>0.10492283789961546</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>54.288928790724519</v>
+        <v>55.637212899182018</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6583,11 +6583,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>25.017939534896097</v>
+        <v>25.639268617134576</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>29.226598159949372</v>
+        <v>29.847927242187851</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6604,11 +6604,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>31.358226016302986</v>
+        <v>32.137018281115978</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>36.197435095021866</v>
+        <v>36.976227359834859</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6651,11 +6651,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>38.912153936392336</v>
+        <v>39.878550583865945</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>44.461141126051231</v>
+        <v>45.42753777352484</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6672,11 +6672,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>44.00675747123249</v>
+        <v>45.0996803393909</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>50.015220493730425</v>
+        <v>51.108143361888835</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14814,7 +14814,7 @@
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
         <f>DCF!F15&amp;"yrs Projection"</f>
-        <v>5yrs Projection</v>
+        <v>11yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591302</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
@@ -15047,7 +15047,8 @@
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
-        <v>0.3</v>
+        <f>C119</f>
+        <v>0.30997621913985418</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
@@ -16314,7 +16315,7 @@
       </c>
       <c r="F14" s="309" t="str">
         <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
         <v>411</v>
@@ -16330,11 +16331,11 @@
       </c>
       <c r="E15" s="308" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
-        <v>Change year</v>
+        <v>Terminal Year</v>
       </c>
       <c r="F15" s="310">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>427</v>
@@ -16374,7 +16375,7 @@
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591302</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>410</v>
@@ -16400,7 +16401,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>54.301934005978339</v>
+        <v>55.650120660393064</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16664,7 +16665,7 @@
     <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B25" s="117">
         <v>5</v>
@@ -16679,11 +16680,11 @@
       </c>
       <c r="E25" s="299">
         <f t="shared" si="6"/>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591299</v>
       </c>
       <c r="F25" s="277">
         <f t="shared" si="7"/>
-        <v>5456612642.2758121</v>
+        <v>5638067187.2112865</v>
       </c>
       <c r="G25" s="299">
         <f t="shared" si="2"/>
@@ -16691,15 +16692,15 @@
       </c>
       <c r="H25" s="277">
         <f t="shared" si="8"/>
-        <v>4092457562.2873011</v>
+        <v>4228548470.9889069</v>
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
-        <v>-9.095693339885802E-3</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
-        <v>0.15151758483457917</v>
+        <v>0.15655616263057856</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16707,7 +16708,7 @@
       </c>
       <c r="L25" s="277">
         <f t="shared" si="4"/>
-        <v>2884016098.6945519</v>
+        <v>2979921399.0202656</v>
       </c>
       <c r="N25" s="275"/>
       <c r="O25" s="275"/>
@@ -16721,7 +16722,7 @@
     <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B26" s="117">
         <v>6</v>
@@ -16736,11 +16737,11 @@
       </c>
       <c r="E26" s="299">
         <f t="shared" si="6"/>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591299</v>
       </c>
       <c r="F26" s="277">
         <f t="shared" si="7"/>
-        <v>5586785141.3773603</v>
+        <v>5772568450.9028997</v>
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
@@ -16748,7 +16749,7 @@
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>4190086890.8239479</v>
+        <v>4329424372.9681025</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
@@ -16756,7 +16757,7 @@
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>0.15151758483457914</v>
+        <v>0.15655616263057853</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16764,13 +16765,13 @@
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>2753209275.3359561</v>
+        <v>2844764715.1721473</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B27" s="117">
         <v>7</v>
@@ -16785,11 +16786,11 @@
       </c>
       <c r="E27" s="299">
         <f t="shared" si="6"/>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591299</v>
       </c>
       <c r="F27" s="277">
         <f t="shared" si="7"/>
-        <v>5720063024.8323927</v>
+        <v>5910278365.5974102</v>
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
@@ -16797,7 +16798,7 @@
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>4290045256.5333576</v>
+        <v>4432706762.1071205</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
@@ -16805,7 +16806,7 @@
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>0.15151758483457917</v>
+        <v>0.15655616263057853</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -16813,13 +16814,13 @@
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>2628335298.5536733</v>
+        <v>2715738169.2514353</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B28" s="117">
         <v>8</v>
@@ -16834,11 +16835,11 @@
       </c>
       <c r="E28" s="299">
         <f t="shared" si="6"/>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591299</v>
       </c>
       <c r="F28" s="277">
         <f t="shared" si="7"/>
-        <v>5856520374.4327564</v>
+        <v>6051273476.6072969</v>
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
@@ -16846,15 +16847,15 @@
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>4392388220.7333565</v>
+        <v>4538453047.3642616</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759698E-2</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
-        <v>0.15151758483457919</v>
+        <v>0.15655616263057856</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -16862,13 +16863,13 @@
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>2509125079.4149199</v>
+        <v>2592563724.0206113</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B29" s="117">
         <v>9</v>
@@ -16883,11 +16884,11 @@
       </c>
       <c r="E29" s="299">
         <f t="shared" si="6"/>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591299</v>
       </c>
       <c r="F29" s="277">
         <f t="shared" si="7"/>
-        <v>5996233039.2593899</v>
+        <v>6195632155.3036747</v>
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
@@ -16895,15 +16896,15 @@
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>4497172670.2079649</v>
+        <v>4646722007.2411795</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>0.15151758483457914</v>
+        <v>0.15655616263057853</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -16911,13 +16912,13 @@
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>2395321733.7275586</v>
+        <v>2474975952.8402176</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B30" s="117">
         <v>10</v>
@@ -16932,11 +16933,11 @@
       </c>
       <c r="E30" s="299">
         <f t="shared" si="6"/>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591299</v>
       </c>
       <c r="F30" s="277">
         <f t="shared" si="7"/>
-        <v>6139278677.8426199</v>
+        <v>6343434642.6785936</v>
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
@@ -16944,7 +16945,7 @@
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>4604456848.8276148</v>
+        <v>4757573822.4545956</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
@@ -16952,7 +16953,7 @@
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
-        <v>0.15151758483457917</v>
+        <v>0.15655616263057853</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -16960,7 +16961,7 @@
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>2286680028.4844675</v>
+        <v>2362721467.7052407</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -18017,11 +18018,11 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591302</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>6200671464.6210461</v>
+        <v>6406868989.1053801</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18029,11 +18030,11 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>64144847135.391594</v>
+        <v>66277924974.884712</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
-        <v>9.9999999999997868E-3</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="J51" s="454"/>
       <c r="K51" s="119">
@@ -18042,7 +18043,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>31855818327.852577</v>
+        <v>32915154239.755772</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18055,7 +18056,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>60716849896.561722</v>
+        <v>62290183722.263702</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18079,7 +18080,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>60716849896.561722</v>
+        <v>62290183722.263702</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18114,19 +18115,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>50751482777.32428</v>
+        <v>52322644744.186913</v>
       </c>
       <c r="C56" s="118">
-        <v>51258997605.097519</v>
+        <v>52845871191.628769</v>
       </c>
       <c r="D56" s="118">
-        <v>51766512432.87075</v>
+        <v>53369097639.070648</v>
       </c>
       <c r="E56" s="118">
-        <v>52274027260.643997</v>
+        <v>53892324086.512527</v>
       </c>
       <c r="F56" s="118">
-        <v>53289056916.190498</v>
+        <v>54938776981.396271</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18140,19 +18141,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>50719860338.565666</v>
+        <v>52289970730.339119</v>
       </c>
       <c r="C57" s="118">
-        <v>51703936222.720543</v>
+        <v>53305605833.368668</v>
       </c>
       <c r="D57" s="118">
-        <v>52697455221.346107</v>
+        <v>54330998072.947205</v>
       </c>
       <c r="E57" s="118">
-        <v>53700417334.44236</v>
+        <v>55366147449.074821</v>
       </c>
       <c r="F57" s="118">
-        <v>55734670904.046883</v>
+        <v>57465717610.977119</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18166,19 +18167,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>50690375547.182335</v>
+        <v>52259505449.362144</v>
       </c>
       <c r="C58" s="118">
-        <v>52122946016.472771</v>
+        <v>53738549412.070068</v>
       </c>
       <c r="D58" s="118">
-        <v>53582827383.81218</v>
+        <v>55245812471.59906</v>
       </c>
       <c r="E58" s="118">
-        <v>55070283792.262665</v>
+        <v>56781567554.845589</v>
       </c>
       <c r="F58" s="118">
-        <v>58128978304.745438</v>
+        <v>59939645500.077255</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18192,19 +18193,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>50662883900.204865</v>
+        <v>52231099592.973358</v>
       </c>
       <c r="C59" s="118">
-        <v>52517537990.076256</v>
+        <v>54146263178.492844</v>
       </c>
       <c r="D59" s="118">
-        <v>54424859650.21347</v>
+        <v>56115845745.841362</v>
       </c>
       <c r="E59" s="118">
-        <v>56385866497.675194</v>
+        <v>58140898751.996078</v>
       </c>
       <c r="F59" s="118">
-        <v>60473055480.254517</v>
+        <v>62361672804.09137</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18218,19 +18219,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>50742408171.847694</v>
+        <v>52204613945.990814</v>
       </c>
       <c r="C60" s="118">
-        <v>52996406268.270233</v>
+        <v>54530217401.417786</v>
       </c>
       <c r="D60" s="118">
-        <v>55335079426.20192</v>
+        <v>56943289978.687187</v>
       </c>
       <c r="E60" s="118">
-        <v>57760878156.298645</v>
+        <v>59446363677.930832</v>
       </c>
       <c r="F60" s="118">
-        <v>62883892365.104073</v>
+        <v>64732888346.482811</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18244,19 +18245,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>50718507717.512009</v>
+        <v>52179918704.049042</v>
       </c>
       <c r="C61" s="118">
-        <v>53346348528.764717</v>
+        <v>54891796669.626816</v>
       </c>
       <c r="D61" s="118">
-        <v>56096692649.311035</v>
+        <v>57730229948.386719</v>
       </c>
       <c r="E61" s="118">
-        <v>58974261428.219269</v>
+        <v>60700096893.513847</v>
       </c>
       <c r="F61" s="118">
-        <v>65130648325.785675</v>
+        <v>67054358108.264641</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18270,19 +18271,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>50794271870.968582</v>
+        <v>52156892837.436676</v>
       </c>
       <c r="C62" s="118">
-        <v>53776917824.517647</v>
+        <v>55232304884.909927</v>
       </c>
       <c r="D62" s="118">
-        <v>56925074446.322685</v>
+        <v>58478648381.107956</v>
       </c>
       <c r="E62" s="118">
-        <v>60246702658.359619</v>
+        <v>61904148373.281219</v>
       </c>
       <c r="F62" s="118">
-        <v>67443773472.617096</v>
+        <v>69327125707.211899</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18296,19 +18297,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>50773493497.16214</v>
+        <v>52135423497.937958</v>
       </c>
       <c r="C63" s="118">
-        <v>54087262671.529282</v>
+        <v>55552969964.104263</v>
       </c>
       <c r="D63" s="118">
-        <v>57613949118.660034</v>
+        <v>59190430946.493195</v>
       </c>
       <c r="E63" s="118">
-        <v>61365825734.787659</v>
+        <v>63060486857.346848</v>
       </c>
       <c r="F63" s="118">
-        <v>69597248793.139313</v>
+        <v>71552212867.020386</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18322,19 +18323,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>50845540663.183151</v>
+        <v>52115405465.771317</v>
       </c>
       <c r="C64" s="118">
-        <v>54474655152.435791</v>
+        <v>55854948267.12178</v>
       </c>
       <c r="D64" s="118">
-        <v>58368059619.969276</v>
+        <v>59867371008.677727</v>
       </c>
       <c r="E64" s="118">
-        <v>62543496351.381012</v>
+        <v>64171003070.482132</v>
       </c>
       <c r="F64" s="118">
-        <v>71816669035.061218</v>
+        <v>73730619876.623108</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18348,19 +18349,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>50827476537.205627</v>
+        <v>52096740633.914322</v>
       </c>
       <c r="C65" s="118">
-        <v>54749883197.001137</v>
+        <v>56139328766.933151</v>
       </c>
       <c r="D65" s="118">
-        <v>58991142701.760635</v>
+        <v>60511174144.741364</v>
       </c>
       <c r="E65" s="118">
-        <v>63575681720.321648</v>
+        <v>65237512813.633041</v>
       </c>
       <c r="F65" s="118">
-        <v>73880736533.825745</v>
+        <v>75863326039.870514</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18374,19 +18375,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>50992729014.604103</v>
+        <v>52020720696.281975</v>
       </c>
       <c r="C66" s="277">
-        <v>56156743858.5214</v>
+        <v>57331137235.378807</v>
       </c>
       <c r="D66" s="118">
-        <v>61946578752.534752</v>
+        <v>63287210189.270081</v>
       </c>
       <c r="E66" s="118">
-        <v>68439400963.536087</v>
+        <v>69968637223.462753</v>
       </c>
       <c r="F66" s="118">
-        <v>83889002839.14035</v>
+        <v>85874205541.946045</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18409,19 +18410,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>51074403066.438637</v>
+        <v>51967148308.39119</v>
       </c>
       <c r="C67" s="277">
-        <v>57156345274.868546</v>
+        <v>58213865091.199905</v>
       </c>
       <c r="D67" s="118">
-        <v>64194945181.028084</v>
+        <v>65447139088.824402</v>
       </c>
       <c r="E67" s="118">
-        <v>72351725639.069794</v>
+        <v>73833766174.000885</v>
       </c>
       <c r="F67" s="118">
-        <v>92805186661.855423</v>
+        <v>94878137926.798477</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18444,19 +18445,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>51206168964.901062</v>
+        <v>51929395044.790771</v>
       </c>
       <c r="C68" s="277">
-        <v>57976797471.129341</v>
+        <v>58867668523.607773</v>
       </c>
       <c r="D68" s="118">
-        <v>66030516690.295639</v>
+        <v>67127698266.117767</v>
       </c>
       <c r="E68" s="118">
-        <v>75640466709.70015</v>
+        <v>76991413386.416016</v>
       </c>
       <c r="F68" s="118">
-        <v>100930253350.52116</v>
+        <v>102976407252.10461</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18479,19 +18480,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>51274515080.81057</v>
+        <v>51902789754.853203</v>
       </c>
       <c r="C69" s="277">
-        <v>58553065983.813309</v>
+        <v>59351916217.174316</v>
       </c>
       <c r="D69" s="118">
-        <v>67418910189.479568</v>
+        <v>68435277950.323006</v>
       </c>
       <c r="E69" s="118">
-        <v>78277289819.657257</v>
+        <v>79571077880.322479</v>
       </c>
       <c r="F69" s="118">
-        <v>108161249520.53519</v>
+        <v>110260109890.24582</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18619,23 +18620,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.762630561901695</v>
+        <v>47.108956154757422</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.197519017577136</v>
+        <v>47.557307866361413</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>46.63240747325257</v>
+        <v>48.005659577965424</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>47.067295928928019</v>
+        <v>48.454011289569436</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>47.937072840278923</v>
+        <v>49.350714712777439</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18650,23 +18651,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>45.735533356453011</v>
+        <v>47.080957856687334</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>46.578786042104149</v>
+        <v>47.951253574793206</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>47.43013051393411</v>
+        <v>48.8299101639779</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>48.289566771942894</v>
+        <v>49.716927624241492</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>50.032714646496899</v>
+        <v>51.516045158005241</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18681,23 +18682,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>45.710267896827197</v>
+        <v>47.054852217461139</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>46.937834708558505</v>
+        <v>48.322242074108885</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>48.18880417500187</v>
+        <v>49.613812819206565</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>49.463402639826619</v>
+        <v>50.929798323273857</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>52.084391939297717</v>
+        <v>53.635949090396103</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18712,23 +18713,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>45.686710358714535</v>
+        <v>47.030511295105704</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>47.275959793051634</v>
+        <v>48.671611197007579</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>48.910339964548818</v>
+        <v>50.359342617186257</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>50.590722867258094</v>
+        <v>52.094606547053196</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>54.09302705113069</v>
+        <v>55.711379513715826</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18743,23 +18744,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>45.754854550353635</v>
+        <v>47.007815796406014</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>47.686301076851102</v>
+        <v>49.00062081390984</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>49.6903054966726</v>
+        <v>51.068377949530579</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>51.768967647569532</v>
+        <v>53.213256869190943</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>56.15886842632311</v>
+        <v>57.743269438644226</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18774,23 +18775,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>45.734374298137972</v>
+        <v>46.986654492257109</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>47.986165910179707</v>
+        <v>49.310457376214067</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>50.342930366517599</v>
+        <v>51.742705258613299</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>52.808713381863129</v>
+        <v>54.28757839068453</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>58.084109180977443</v>
+        <v>59.732532302210487</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18806,23 +18807,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>45.799296451913953</v>
+        <v>46.966923672537852</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>48.355119891116239</v>
+        <v>49.602238194794282</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>51.052769095747806</v>
+        <v>52.384023538580081</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>53.899065764159914</v>
+        <v>55.319327730673713</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>60.066221560438819</v>
+        <v>61.680062378429227</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18837,23 +18838,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>45.781491504350591</v>
+        <v>46.948526637834583</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>48.621053778872565</v>
+        <v>49.877015469168178</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>51.643064444794376</v>
+        <v>52.993948616031012</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>54.858040122710079</v>
+        <v>56.310191898681964</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>61.911530318384166</v>
+        <v>63.586735180321675</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18869,23 +18870,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>45.843228578918726</v>
+        <v>46.931373225523835</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>48.953009632262891</v>
+        <v>50.135780081865278</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>52.289260247115919</v>
+        <v>53.574017221159153</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>55.867183753038574</v>
+        <v>57.261791053039531</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>63.813347149508338</v>
+        <v>65.453407853503094</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18901,23 +18902,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>45.827749464970545</v>
+        <v>46.915379367891454</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>49.188852001213483</v>
+        <v>50.379465171677936</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>52.823178911890004</v>
+        <v>54.125690859602713</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>56.751661361385302</v>
+        <v>58.175681149998326</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>65.582042521200307</v>
+        <v>67.280919561512874</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18933,23 +18934,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>45.969353987162897</v>
+        <v>46.850238033159364</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>50.394388129337102</v>
+        <v>51.400723499394864</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>55.355686239031492</v>
+        <v>56.504470674965795</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>60.919372795159468</v>
+        <v>62.229772332371688</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>74.158106193277945</v>
+        <v>75.859222476744691</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18965,23 +18966,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>46.039340321211341</v>
+        <v>46.804331959559718</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>51.250944612925061</v>
+        <v>52.15713125931012</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>57.282307000379681</v>
+        <v>58.355309492064613</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>64.271836098958701</v>
+        <v>65.541793712438647</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>81.798366538363695</v>
+        <v>83.574674391785337</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18997,23 +18998,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>46.152250259910936</v>
+        <v>46.771981262387122</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>51.953988482900037</v>
+        <v>52.717374131981813</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>58.855204609006549</v>
+        <v>59.795377338931253</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>67.089951840715642</v>
+        <v>68.247575385459314</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>88.760720170468019</v>
+        <v>90.514065416040808</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19029,23 +19030,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.210815911932791</v>
+        <v>46.749183241875066</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>52.447791835671218</v>
+        <v>53.132325026211923</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>60.044916262120459</v>
+        <v>60.915839793263075</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>69.349440366814278</v>
+        <v>70.458084806116105</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>94.956946537232383</v>
+        <v>96.75545585146601</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19092,7 +19093,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>65.582042521200307</v>
+        <v>67.280919561512874</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19120,7 +19121,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>56.751661361385302</v>
+        <v>58.175681149998326</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19148,7 +19149,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>52.823178911890004</v>
+        <v>54.125690859602713</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19176,7 +19177,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>49.188852001213483</v>
+        <v>50.379465171677936</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19204,7 +19205,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>45.827749464970545</v>
+        <v>46.915379367891454</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19564,7 +19565,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>56.751661361385302</v>
+        <v>58.175681149998326</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19588,7 +19589,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>52.823178911890004</v>
+        <v>54.125690859602713</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19611,7 +19612,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>49.188852001213483</v>
+        <v>50.379465171677936</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19627,7 +19628,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>52.700293674119933</v>
+        <v>53.999132495700636</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19674,7 +19675,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>65.582042521200307</v>
+        <v>67.280919561512874</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19697,7 +19698,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>45.827749464970545</v>
+        <v>46.915379367891454</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19753,7 +19754,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>8.05651608340405E-2</v>
+        <v>8.8713270485525436E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19773,7 +19774,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>4.2176042556715192E-2</v>
+        <v>5.0050795628677404E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19782,7 +19783,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>54.288928790724519</v>
+        <v>55.637212899182018</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19808,7 +19809,7 @@
     <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
-        <v>2-stage DCF</v>
+        <v>1-stage DCF</v>
       </c>
       <c r="E39" s="222" t="s">
         <v>251</v>
@@ -19820,7 +19821,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591302</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>399</v>
@@ -19885,7 +19886,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>54.301934005978339</v>
+        <v>55.650120660393064</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19901,7 +19902,7 @@
       </c>
       <c r="C49" s="218" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Negative Growth </v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="E49" s="222" t="s">
         <v>254</v>
@@ -19913,7 +19914,7 @@
       </c>
       <c r="C50" s="218" t="str">
         <f>IF(C36&lt;C35,"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E50" s="126"/>
     </row>
@@ -19923,7 +19924,7 @@
       </c>
       <c r="C51" s="218" t="str">
         <f>IF(C50="Y","N",IF(C46&gt;8%,"N","Y"))</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E51" s="221" t="s">
         <v>247</v>
@@ -19952,7 +19953,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>4.1883032968331749E-2</v>
+        <v>4.0868060707454294E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20030,11 +20031,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>25.017939534896097</v>
+        <v>25.639268617134576</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>29.226598159949372</v>
+        <v>29.847927242187851</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20042,7 +20043,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46164717538241695</v>
+        <v>0.46352583663250546</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20055,11 +20056,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>31.358226016302986</v>
+        <v>32.137018281115978</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>36.197435095021866</v>
+        <v>36.976227359834859</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20067,7 +20068,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.33324462461660609</v>
+        <v>0.33540475101011957</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20101,11 +20102,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>38.912153936392336</v>
+        <v>39.878550583865945</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>44.461141126051231</v>
+        <v>45.42753777352484</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20113,7 +20114,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18102747435960465</v>
+        <v>0.18350443154220764</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20126,11 +20127,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>44.00675747123249</v>
+        <v>45.0996803393909</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>50.015220493730425</v>
+        <v>51.108143361888835</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20138,7 +20139,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>7.8721544008882205E-2</v>
+        <v>8.1403602037005918E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20274,7 +20275,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>8.05651608340405E-2</v>
+        <v>8.8713270485525436E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20282,13 +20283,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20352,7 +20353,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>54.288928790724519</v>
+        <v>55.637212899182018</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>360</v>
@@ -20368,7 +20369,7 @@
       </c>
       <c r="C19" s="352" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Negative Growth </v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="343" t="s">
         <v>361</v>
@@ -20404,7 +20405,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>29.226598159949372</v>
+        <v>29.847927242187851</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>438</v>
@@ -20420,7 +20421,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>36.197435095021866</v>
+        <v>36.976227359834859</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>439</v>
@@ -20436,7 +20437,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>44.461141126051231</v>
+        <v>45.42753777352484</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>441</v>
@@ -20452,7 +20453,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>50.015220493730425</v>
+        <v>51.108143361888835</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>440</v>
@@ -20473,22 +20474,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20678,10 +20679,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20697,22 +20698,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20783,7 +20784,7 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.3</v>
+        <v>0.30997621913985418</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
@@ -20797,7 +20798,7 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.20202354119791383</v>
+        <v>0.20874164492591302</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
@@ -20847,22 +20848,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20870,13 +20871,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21025,33 +21026,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21114,23 +21115,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21174,13 +21175,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21225,7 +21226,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>65.58 CNY</v>
+        <v>67.28 CNY</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21248,7 +21249,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>56.75 CNY</v>
+        <v>58.18 CNY</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21270,7 +21271,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>52.82 CNY</v>
+        <v>54.13 CNY</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21292,7 +21293,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>49.19 CNY</v>
+        <v>50.38 CNY</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21314,7 +21315,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.83 CNY</v>
+        <v>46.92 CNY</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21336,7 +21337,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>54.288928790724519</v>
+        <v>55.637212899182018</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21344,13 +21345,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21363,22 +21364,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21443,11 +21444,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>25.017939534896097</v>
+        <v>25.639268617134576</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>29.226598159949372</v>
+        <v>29.847927242187851</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21464,11 +21465,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>31.358226016302986</v>
+        <v>32.137018281115978</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>36.197435095021866</v>
+        <v>36.976227359834859</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21504,11 +21505,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>38.912153936392336</v>
+        <v>39.878550583865945</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>44.461141126051231</v>
+        <v>45.42753777352484</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21525,11 +21526,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>44.00675747123249</v>
+        <v>45.0996803393909</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>50.015220493730425</v>
+        <v>51.108143361888835</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21547,13 +21548,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21561,13 +21562,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21604,22 +21605,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21643,15 +21644,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21666,12 +21664,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/not_monitored/300979.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/not_monitored/300979.SZ_Valuation.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579A54EE-2C76-4952-9746-C86F4DD17E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20283,13 +20283,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20474,22 +20474,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20679,10 +20679,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20698,22 +20698,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20848,22 +20848,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20871,13 +20871,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21026,33 +21026,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21115,23 +21115,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21175,13 +21175,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21345,13 +21345,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21364,22 +21364,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21548,13 +21548,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21562,13 +21562,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21605,22 +21605,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21644,12 +21644,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21664,15 +21667,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
